--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Database engine used for the relational database.</t>
+          <t>AWS service implementing the MySQL database.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,131 +513,131 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.1751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Communication between Web Socket and Cloud Services.</t>
+          <t>Backend framework used for developing microservices.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46, 60</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_10, AU_12</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>web socket, cloud services</t>
-        </is>
-      </c>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.5609</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication between Core and Database.</t>
+          <t>Programming language used for development.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_07, AU_11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>core, database</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M01_AU15</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>SQL database</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.3809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_28</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -648,48 +648,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Communication between Core and Cloud Services.</t>
+          <t>The Web Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_07, AU_12</t>
+          <t>AU_04, AU_06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>core, cloud services</t>
+          <t>web platform, api gateway</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.4473</v>
+        <v>0.4804</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -700,48 +700,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Communication between Analytics Module and Cloud Services.</t>
+          <t>The Mobile Platform communicates with the API Gateway.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_08, AU_12</t>
+          <t>AU_05, AU_06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>analytics module, cloud services</t>
+          <t>mobile platform, api gateway</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AD04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.466</v>
+        <v>0.4672</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Communication between Analytics Module and Database.</t>
+          <t>The Web Socket service communicates with the Database.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -762,476 +762,444 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08, AU_11</t>
+          <t>AU_10, AU_11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>analytics module, database</t>
+          <t>web socket, database</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.476</v>
+        <v>0.5787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TCP</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Protocol used for communication between microservices.</t>
+          <t>The Web Socket service communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_22, AU_23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>AU_10, AU_13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>web socket, cloud services set</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Web Socket</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.4804</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NestJS</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>The Core service communicates with the Database.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8, 46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>AU_07, AU_11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>core, database</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Programming language used for development.</t>
+          <t>The Core service communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8, 46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>AU_07, AU_13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>core, cloud services set</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technical support department of Waapiti.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9, 10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_08, AU_11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>analytical module, database</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>CF_M01_AU12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Analytical module</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.0287</v>
+        <v>0.6383</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stakeholder responsible for product value and requirements.</t>
+          <t>The Analytical Module communicates with the Cloud Services Set.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_08, AU_13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>analytical module, cloud services set</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.0319</v>
+        <v>0.5977</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
+          <t>AU_35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Author of the project responsible for design and implementation.</t>
+          <t>The Cloud Services Set communicates with the Database.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_13, AU_11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cloud services set, database</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>AWS cloud services suite</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.0227</v>
+        <v>0.3671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_38</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clients</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>External beneficiaries of the platform.</t>
+          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>AWS cloud services suite</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.4613</v>
+        <v>0.2282</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Data Lake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
+          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
+          <t>8, 47</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>AWS cloud services suite</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.2781</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>8, 47</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0.441</v>
+        <v>0.4246</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -496,12 +496,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AWS service implementing the MySQL database.</t>
+          <t>AWS service hosting the MySQL database.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,21 +513,21 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="3">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.0755</v>
+        <v>0.0762</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -637,215 +637,195 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The Web Platform communicates with the API Gateway.</t>
+          <t>Technical support department of Waapiti.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AU_04, AU_06</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>web platform, api gateway</t>
-        </is>
-      </c>
+          <t>9, 10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>API Gateway</t>
-        </is>
-      </c>
+          <t>CF_M01_AU26</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.4804</v>
+        <v>0.0315</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Mobile Platform communicates with the API Gateway.</t>
+          <t>Stakeholder responsible for product value and investment return.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_05, AU_06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>mobile platform, api gateway</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AD04</t>
+          <t>CF_M01_AU24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This design pattern allows only one component to interact between users and the services provided by the platform.</t>
+          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.4672</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Database.</t>
+          <t>Author of the project responsible for design and implementation.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_10, AU_11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>web socket, database</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_AU30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.5787</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Clients</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Web Socket service communicates with the Cloud Services Set.</t>
+          <t>External beneficiaries of the platform.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AU_10, AU_13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>web socket, cloud services set</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU14</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Web Socket</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players, thus allowing the exchange of information between them. It processes the data coming from the players and stores it in the database and in the cloud services.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4804</v>
+        <v>0.4629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -856,7 +836,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Database.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -866,38 +846,34 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_07, AU_11</t>
+          <t>AU_08, AU_11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>core, database</t>
+          <t>analytical module, database</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Core Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU42</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>The Analytical Module communicates with the Database.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.641</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -908,298 +884,138 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Core service communicates with the Cloud Services Set.</t>
+          <t>The Business Layer communicates with the Data Layer.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_07, AU_13</t>
+          <t>AU_02, AU_03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>core, cloud services set</t>
+          <t>business layer, data layer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Core Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU33</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6042</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_33</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Database.</t>
+          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_08, AU_11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>analytical module, database</t>
-        </is>
-      </c>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.6383</v>
+        <v>0.261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data Lake</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Cloud Services Set.</t>
+          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_08, AU_13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>analytical module, cloud services set</t>
-        </is>
-      </c>
+          <t>8, 47</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.5977</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>The Cloud Services Set communicates with the Database.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_13, AU_11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>cloud services set, database</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.3671</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AWS cloud services suite</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2282</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>8, 47</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0.4246</v>
+        <v>0.4115</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,336 +496,348 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AWS service hosting the MySQL database.</t>
+          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6606</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Cloud Storage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices.</t>
+          <t>Conjunt de serveis cloud AWS: L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46, 60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M01_AU04</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.0762</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Programming language used for development.</t>
+          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_06, AU_07, AU_08, AU_09, AU_10</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_01, AU_04</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>presentation layer, api gateway</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>CF_M01_AU30</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>the presentation layer communicates with the business layer</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technical support department of Waapiti.</t>
+          <t>Servei Core: [...] Principalment, interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9, 10</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_05, AU_09, AU_12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>core, database, cloud storage</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU26</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>CF_M01_AU11</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Core Service</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Furthermore, it can be observed that three components are directly or indirectly related to the presentation layer, that is, they interact with users. These components would be, the Api Gateway, the Core and the analytical module. […] the only component that interacts directly with the presentation layer is the Api Gateway module [...]</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.0315</v>
+        <v>0.7564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stakeholder responsible for product value and investment return.</t>
+          <t>Mòdul analític: [...] Principalment, aquest servei interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_06, AU_12, AU_09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>analytical module, cloud storage, database</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AU24</t>
+          <t>CF_M01_P01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
+          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.0336</v>
+        <v>0.6844</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
+          <t>AU_32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Author of the project responsible for design and implementation.</t>
+          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_08, AU_18, AU_09, AU_12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>web socket, player, database, cloud storage</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.0219</v>
+        <v>0.8249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Clients</t>
-        </is>
-      </c>
+          <t>AU_33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>External beneficiaries of the platform.</t>
+          <t>El microservei WebSocket [...] s’encarrega de rebre la informació dels players. Mentre que l’audit trail té com a generador el Core [...] Per part dels consumidors tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_08, AU_05, AU_25, AU_12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>web socket, core, kinesis data firehose, cloud storage</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.4629</v>
+        <v>0.7445000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_39</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -836,44 +848,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Database.</t>
+          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_08, AU_11</t>
+          <t>AU_22, AU_13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>analytical module, database</t>
+          <t>amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU42</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The Analytical Module communicates with the Database.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.7753</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_41</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -884,138 +900,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Business Layer communicates with the Data Layer.</t>
+          <t>El servei d’AWS Glue [...] treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_02, AU_03</t>
+          <t>AU_23, AU_22, AU_13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>business layer, data layer</t>
+          <t>aws glue, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CF_M01_AU33</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.745</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The business and data layers are divided into several different services to improve security, scalability, and availability.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU16</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AWS cloud services set</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.261</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>P_05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Data Lake</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A centralized repository that allows for the storage of structured and unstructured data at any scale without needing to modify or structure it initially.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>8, 47</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4115</v>
+        <v>0.7893</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,105 +481,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Amazon RDS</t>
-        </is>
-      </c>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aquesta base de dades està implementada en el servei RDS, que és un servei de base de dades relacional distribuït d’AWS.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>AU_06, AU_10, AU_11</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>core, database, aws cloud services</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7803</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Cloud Storage</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Conjunt de serveis cloud AWS: L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics.</t>
+          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_03</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>AU_07, AU_11, AU_10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>analytical module, aws cloud services, database</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7937</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="4">
@@ -596,44 +596,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>la capa de presentació es comunica amb la capa de negoci, més concretament amb l’Api Gateway, mitjançant el protocol HTTP.</t>
+          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_01, AU_04</t>
+          <t>AU_09, AU_10, AU_11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>presentation layer, api gateway</t>
+          <t>web socket, database, aws cloud services</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M01_AU30</t>
+          <t>CF_M01_AU29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>the presentation layer communicates with the business layer</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7845</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_29</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -644,48 +644,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Servei Core: [...] Principalment, interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
+          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers. [...] In the case of playlogs the generator is the WebSocket microservice. [...] While the audit trail has as a generator the Core.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_05, AU_09, AU_12</t>
+          <t>AU_18, AU_09, AU_06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>core, database, cloud storage</t>
+          <t>kinesis data streams, web socket, core</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7564</v>
+        <v>0.7364000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -696,42 +696,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mòdul analític: [...] Principalment, aquest servei interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
+          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in S3.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_06, AU_12, AU_09</t>
+          <t>AU_19, AU_11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>analytical module, cloud storage, database</t>
+          <t>kinesis data firehose, aws cloud services</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_P01</t>
+          <t>CF_M01_AU23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Kinesis Data Firehose</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service that follows the client-server architecture. In this type of architecture, the client is the one who makes requests to a server, which processes them and returns the response to the client.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6844</v>
+        <v>0.8252</v>
       </c>
     </row>
     <row r="7">
@@ -748,38 +748,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Web Socket: Aquest servei s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells. Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+          <t>The analytical module uses the AWS Athena service to perform queries on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49,62</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08, AU_18, AU_09, AU_12</t>
+          <t>AU_07, AU_16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>web socket, player, database, cloud storage</t>
+          <t>analytical module, amazon athena</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.8249</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="8">
@@ -796,146 +800,94 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>El microservei WebSocket [...] s’encarrega de rebre la informació dels players. Mentre que l’audit trail té com a generador el Core [...] Per part dels consumidors tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
+          <t>The analytical module also has the database service, which is responsible for connecting and performing queries to the platform's database.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_08, AU_05, AU_25, AU_12</t>
+          <t>AU_07, AU_10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>web socket, core, kinesis data firehose, cloud storage</t>
+          <t>analytical module, database</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
+          <t>L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema... les diferents capes que formen el sistema es componen de diversos serveis que interactuen entre si.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_22, AU_13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>amazon athena, amazon s3</t>
-        </is>
-      </c>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.7753</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AU_35</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>El servei d’AWS Glue [...] treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_23, AU_22, AU_13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>aws glue, amazon athena, amazon s3</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7893</v>
+        <v>0.7454</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_25</t>
+          <t>AU_26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>Principalment, [Core] interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_06, AU_10, AU_11</t>
+          <t>AU_06, AU_10, AU_13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7699</v>
+        <v>0.7533</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_26</t>
+          <t>AU_27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>Principalment, aquest servei [Analytical Module] interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_07, AU_11, AU_10</t>
+          <t>AU_07, AU_13, AU_10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -579,13 +579,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7214</v>
+        <v>0.7271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_27</t>
+          <t>AU_28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_09, AU_10, AU_11</t>
+          <t>AU_09, AU_10, AU_13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.799</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers. [...] In the case of playlogs the generator is the WebSocket microservice. [...] While the audit trail has as a generator the Core.</t>
+          <t>En el cas dels generadors [de Kinesis Data Streams], aquests serien els diferents microserveis de NestJS que tenen la informació sobre els playlogs o les accions en plataforma. En el cas dels playlogs el generador el microservei WebSocket [...] Mentre que l’audit trail té com a generador el Core.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in S3.</t>
+          <t>Per part dels consumidors [de Kinesis Data Streams] tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_19, AU_11</t>
+          <t>AU_18, AU_19, AU_14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kinesis data firehose, aws cloud services</t>
+          <t>kinesis data streams, kinesis data firehose, amazon s3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8252</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -748,22 +748,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The analytical module uses the AWS Athena service to perform queries on data stored in Amazon S3.</t>
+          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49,62</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_07, AU_16</t>
+          <t>AU_16, AU_14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>analytical module, amazon athena</t>
+          <t>amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -783,13 +783,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7654</v>
+        <v>0.7753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -800,42 +800,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The analytical module also has the database service, which is responsible for connecting and performing queries to the platform's database.</t>
+          <t>L’ús d’aquesta [AWS Glue Data Catalog] ha sigut necessària per poder emmagatzemar les metadades de les dades del projecte [...] D’aquesta manera treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_07, AU_10</t>
+          <t>AU_17, AU_16, AU_14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>analytical module, database</t>
+          <t>aws glue, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>AWS Glue</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7284</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="9">

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,105 +481,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Principalment, [Core] interactua amb la base de dades, encara que també interactua en menor mesura amb els serveis cloud.</t>
+          <t>The client is the user of the platform.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AU_06, AU_10, AU_13</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>core, database, aws cloud services</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7533</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data Lake Service</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Principalment, aquest servei [Analytical Module] interactua amb els serveis cloud, encara que també interactua en menor mesura amb la base de dades.</t>
+          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_07, AU_13, AU_10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>analytical module, aws cloud services, database</t>
-        </is>
-      </c>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7271</v>
+        <v>0.7272999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -588,46 +584,46 @@
           <t>AU_28</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AWS CDK</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players [...] Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
+          <t>AWS Cloud Development, also called AWS CDK, is the AWS framework that allows the construction of cloud applications.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AU_09, AU_10, AU_13</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>web socket, database, aws cloud services</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>CF_M01_AU18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8186</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="5">
@@ -636,56 +632,52 @@
           <t>AU_29</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>En el cas dels generadors [de Kinesis Data Streams], aquests serien els diferents microserveis de NestJS que tenen la informació sobre els playlogs o les accions en plataforma. En el cas dels playlogs el generador el microservei WebSocket [...] Mentre que l’audit trail té com a generador el Core.</t>
+          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AU_18, AU_09, AU_06</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>kinesis data streams, web socket, core</t>
-        </is>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kinesis Data Streams</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.699</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_30</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -696,48 +688,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Per part dels consumidors [de Kinesis Data Streams] tenim el servei de Kinesis Data Firehose, que s’encarrega de guardar les dades en el S3.</t>
+          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_18, AU_19, AU_14</t>
+          <t>AU_07, AU_08, AU_09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>kinesis data streams, kinesis data firehose, amazon s3</t>
+          <t>api gateway, core, analytical module</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8393</v>
+        <v>0.8048999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_31</t>
+          <t>AU_34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -748,48 +740,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>El servei d’Amazon Athena és un servei que permet realitzar consultes en SQL sobre dades emmagatzemades en Amazon S3.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_16, AU_14</t>
+          <t>AU_08, AU_12, AU_20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>amazon athena, amazon s3</t>
+          <t>core, database service, aws</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7753</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_32</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -800,93 +792,345 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>L’ús d’aquesta [AWS Glue Data Catalog] ha sigut necessària per poder emmagatzemar les metadades de les dades del projecte [...] D’aquesta manera treballa en conjunt amb Athena perquè pugui llegir les dades des del S3 de manera correcta.</t>
+          <t>The Analytical Module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_17, AU_16, AU_14</t>
+          <t>AU_09, AU_20, AU_12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>aws glue, amazon athena, amazon s3</t>
+          <t>analytical module, aws, database service</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU21</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AWS Glue</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7289</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
+          <t>AU_37</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema... les diferents capes que formen el sistema es componen de diversos serveis que interactuen entre si.</t>
+          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>AU_11, AU_30, AU_12, AU_20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>web socket, player, database service, aws</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>This service is responsible for communicating between the platform and the players.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8564000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AU_38</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The Analytical Module uses the Amazon Athena service to perform queries on data stored in Amazon S3.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_09, AU_24, AU_16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>analytical module, amazon athena, amazon s3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CF_M01_AU17</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Amazon S3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7613</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AU_39</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The AWS Glue service works in conjunction with Athena so that it can read data from S3 correctly.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_25, AU_24, AU_16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>aws glue, amazon athena, amazon s3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CF_M01_AU21</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AWS Glue</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8133</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AU_40</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers (Consumers). [...] In the case of the playlogs the generator is the WebSocket microservice [...] while the audit trail has as generator the Core.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50,51</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AU_26, AU_11, AU_08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>kinesis data streams, web socket, core</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CF_M01_AU22</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Kinesis Data Streams</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AU_41</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in the S3.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AU_27, AU_26, AU_16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8238</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L14" t="n">
         <v>0.7454</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,7 +534,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Lake Service</t>
+          <t>Data Lake</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_04, P_04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -575,109 +575,117 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AWS CDK</t>
-        </is>
-      </c>
+          <t>AU_30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AWS Cloud Development, also called AWS CDK, is the AWS framework that allows the construction of cloud applications.</t>
+          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_08, AU_12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>core, relational database</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M01_AU18</t>
+          <t>CF_M01_AU11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Core Service</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
+          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7153</v>
+        <v>0.7699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AWS CloudFormation</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
+          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_09, AU_15</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>analytical module, data lake</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU16</t>
+          <t>CF_M01_AU12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AWS cloud services set</t>
+          <t>Analytical module</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
+          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7708</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_33</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -688,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The communication between the Api Gateway service is through the TCP communication protocol.</t>
+          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -698,38 +706,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_07, AU_08, AU_09</t>
+          <t>AU_11, AU_12, AU_15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>api gateway, core, analytical module</t>
+          <t>web socket, relational database, data lake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>API Gateway Service</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -740,48 +744,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>The analytical module uses Amazon Athena to perform queries on data stored in Amazon S3.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_08, AU_12, AU_20</t>
+          <t>AU_09, AU_23, AU_16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>core, database service, aws</t>
+          <t>analytical module, amazon athena, amazon s3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU17</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7699</v>
+        <v>0.7788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -792,42 +796,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The Analytical Module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>The microservices (Core and Web Socket) send data to the Kinesis Data Stream.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_09, AU_20, AU_12</t>
+          <t>AU_08, AU_11, AU_25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>analytical module, aws, database service</t>
+          <t>core, web socket, kinesis data streams</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Kinesis Data Streams</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7204</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="9">
@@ -844,294 +848,94 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Web Socket service is responsible for carrying out the communication between the platform and the players, and in this way allows the exchange of information between them. [...] It processes the data coming from the players and stores them in the database and in the cloud services.</t>
+          <t>Kinesis Data Firehose reads from the Kinesis Data Stream and saves the data in Amazon S3.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_11, AU_30, AU_12, AU_20</t>
+          <t>AU_26, AU_25, AU_16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>web socket, player, database service, aws</t>
+          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>CF_M01_AU23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_38</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Data lake</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Analytical Module uses the Amazon Athena service to perform queries on data stored in Amazon S3.</t>
+          <t>Un data lake consisteix en un dipòsit de dades que poden ser emmagatzemades en el seu format natural.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_09, AU_24, AU_16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>analytical module, amazon athena, amazon s3</t>
-        </is>
-      </c>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
+          <t>CF_M01_AU07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.7613</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AU_39</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The AWS Glue service works in conjunction with Athena so that it can read data from S3 correctly.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AU_25, AU_24, AU_16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>aws glue, amazon athena, amazon s3</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CF_M01_AU21</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AWS Glue</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Serverless data integration service that allows us to detect, prepare, migrate and integrate data from different sources. In the case of the development of this project we have made use of the AWS Glue Data Catalog function. The use of this has been necessary to be able to store the metadata of the project data</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.8133</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AU_40</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams reads data from different generators (Producers) and sends them to the consumers (Consumers). [...] In the case of the playlogs the generator is the WebSocket microservice [...] while the audit trail has as generator the Core.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50,51</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AU_26, AU_11, AU_08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>kinesis data streams, web socket, core</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7433999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AU_41</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>For the consumers we have the Kinesis Data Firehose service, which is responsible for saving the data in the S3.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AU_27, AU_26, AU_16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CF_M01_AU23</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Kinesis Data Firehose</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.8238</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CF_M01_AU10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>API Gateway Service</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.7454</v>
+        <v>0.7534</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M01_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>LLM_fixes</t>
+          <t>LLM_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -529,211 +529,215 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Lake</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all the history is stored to be able to process them in the analytical module.</t>
+          <t>For the infrastructure, the cloud services of AWS will be used.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_04, P_04</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M01_AU07</t>
+          <t>CF_M01_AU16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>AWS cloud services set</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7526</v>
+        <v>0.8603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Amazon RDS</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Core service interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This database is implemented in the RDS service.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_08, AU_12</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>core, relational database</t>
-        </is>
-      </c>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M01_AU11</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Core Service</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>This service is responsible for carrying out the business logic of the platform, it would be the main core of the platform. Mainly, it interacts with the database, although it also interacts to a lesser extent with cloud services.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7699</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>AU_28</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AWS CDK</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The analytical module interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>The AWS CDK is the AWS framework that allows the construction of applications in the cloud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_09, AU_15</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>analytical module, data lake</t>
-        </is>
-      </c>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M01_AU12</t>
+          <t>CF_M01_AU18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Analytical module</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
+          <t>This service is a non-relational database from AWS. In our case, it is responsible for storing playlogs in real time.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7214</v>
+        <v>0.7153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AU_32</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AWS CloudFormation</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Web Socket service processes data from players and stores it in the database and cloud services.</t>
+          <t>AWS CloudFormation is an Amazon service that helps configure AWS resources.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_11, AU_12, AU_15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>web socket, relational database, data lake</t>
-        </is>
-      </c>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M01_AU29</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>CF_M01_AU16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AWS cloud services set</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This service is responsible for communicating between the platform and the players.</t>
+          <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.799</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_35</t>
+          <t>AU_32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -744,48 +748,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The analytical module uses Amazon Athena to perform queries on data stored in Amazon S3.</t>
+          <t>Aquest servei [Web Socket] s’encarrega de realitzar la comunicació entre la plataforma i els players, i d’aquesta manera permet l’intercanvi d’informació entre ells.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_09, AU_23, AU_16</t>
+          <t>AU_11, AU_10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>analytical module, amazon athena, amazon s3</t>
+          <t>web socket service, player api service</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CF_M01_AU17</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Amazon S3</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This is the AWS object storage service. In this project it is responsible for storing JSON documents containing playlogs, connections and audit trails.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7788</v>
+        <v>0.847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_36</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -796,146 +796,90 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The microservices (Core and Web Socket) send data to the Kinesis Data Stream.</t>
+          <t>Processa les dades provinents dels players i les emmagatzema en la base de dades i en els serveis cloud.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_08, AU_11, AU_25</t>
+          <t>AU_11, AU_12, AU_13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>core, web socket, kinesis data streams</t>
+          <t>web socket service, database, aws cloud services</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CF_M01_AU22</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Kinesis Data Streams</t>
-        </is>
-      </c>
+          <t>CF_M01_AU29</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Data processing and ingestion service aimed especially at data streaming. In the development of this project, Kinesis Data Streams has been used to transmit playlog and audit trail data.</t>
+          <t>This service is responsible for communicating between the platform and the players.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7889</v>
+        <v>0.7296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_37</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose reads from the Kinesis Data Stream and saves the data in Amazon S3.</t>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AU_26, AU_25, AU_16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>kinesis data firehose, kinesis data streams, amazon s3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>The document describes the system as being composed of several different services, which constitutes a microservices architectural style.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M01_AU23</t>
+          <t>CF_M01_AU10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Kinesis Data Firehose</t>
+          <t>API Gateway Service</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Its main function is to load large amounts of data into data warehouses. In this project we have used Kinesis Data Stream to store the playlogs and audit trail data in their corresponding S3 buckets. In addition, we have used one of the functionalities that Kinesis Data Firehose has with respect to the S3 service, which is dynamic partitioning.</t>
+          <t>This service is responsible for the management, authentication and authorization of platform users. It defines all the REST API routes and processes the requests to be sent to the Core service and the analytical module.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.8948</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Data lake</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Un data lake consisteix en un dipòsit de dades que poden ser emmagatzemades en el seu format natural.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M01_AU07</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Data Layer</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>It is the layer that is responsible for storing all the data. In our case, it would be the database and AWS storage services.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7534</v>
+        <v>0.7454</v>
       </c>
     </row>
   </sheetData>
